--- a/French Ligue 1/Træning og forudsigelse/X_pred.xlsx
+++ b/French Ligue 1/Træning og forudsigelse/X_pred.xlsx
@@ -1742,97 +1742,97 @@
         <v>3.233532934131737</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.710082098246945</v>
+        <v>5.741317365269461</v>
       </c>
       <c r="BO2" t="n">
-        <v>35.68801311404341</v>
+        <v>35.88323353293413</v>
       </c>
       <c r="BP2" t="n">
-        <v>10.94432402163998</v>
+        <v>11.00419161676647</v>
       </c>
       <c r="BQ2" t="n">
-        <v>137.5178105327806</v>
+        <v>138.2700598802395</v>
       </c>
       <c r="BR2" t="n">
-        <v>24.26784891754951</v>
+        <v>24.40059880239521</v>
       </c>
       <c r="BS2" t="n">
-        <v>16.65440611988692</v>
+        <v>16.74550898203593</v>
       </c>
       <c r="BT2" t="n">
-        <v>41.39809521229034</v>
+        <v>41.62455089820359</v>
       </c>
       <c r="BU2" t="n">
-        <v>1581.21690103955</v>
+        <v>1589.866467065868</v>
       </c>
       <c r="BV2" t="n">
-        <v>31.40545154035819</v>
+        <v>31.57724550898204</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.37184454620171</v>
+        <v>12.43952095808383</v>
       </c>
       <c r="BX2" t="n">
-        <v>24.26784891754951</v>
+        <v>24.40059880239521</v>
       </c>
       <c r="BY2" t="n">
-        <v>46.63233713568339</v>
+        <v>46.8874251497006</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.855041049123472</v>
+        <v>2.870658682634731</v>
       </c>
       <c r="CA2" t="n">
-        <v>17.60608646959475</v>
+        <v>17.70239520958084</v>
       </c>
       <c r="CB2" t="n">
-        <v>42.82561573685209</v>
+        <v>43.05988023952096</v>
       </c>
       <c r="CC2" t="n">
-        <v>124.670125811725</v>
+        <v>125.3520958083832</v>
       </c>
       <c r="CD2" t="n">
-        <v>1349.958576060548</v>
+        <v>1357.343113772455</v>
       </c>
       <c r="CE2" t="n">
-        <v>1171.518510490331</v>
+        <v>1177.926946107784</v>
       </c>
       <c r="CF2" t="n">
-        <v>203.8975149249013</v>
+        <v>205.012874251497</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.4561336625619824</v>
+        <v>0.4586288030000606</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.909143121955732</v>
+        <v>0.9141163128288878</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.3383752354516708</v>
+        <v>0.3402262142381903</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.8697300973718727</v>
+        <v>0.8744876912840986</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.07365456984693008</v>
+        <v>0.07405747476440996</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.2429820926939437</v>
+        <v>0.2443112523130875</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.038975149249013</v>
+        <v>2.05012874251497</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.350611624779884</v>
+        <v>1.357999734796142</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1135096984950783</v>
+        <v>0.1141306187692767</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.37430972840476</v>
+        <v>1.381827471687566</v>
       </c>
       <c r="CQ2" t="n">
-        <v>1.346398031191336</v>
+        <v>1.353763092025709</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.1029555685027992</v>
+        <v>0.1035187556196057</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -2030,190 +2030,190 @@
         <v>2.103293413173652</v>
       </c>
       <c r="FF2" t="n">
-        <v>6.456244750318368</v>
+        <v>6.442739520958084</v>
       </c>
       <c r="FG2" t="n">
-        <v>49.88916397973284</v>
+        <v>49.78480538922156</v>
       </c>
       <c r="FH2" t="n">
-        <v>13.49942084157477</v>
+        <v>13.47118263473054</v>
       </c>
       <c r="FI2" t="n">
-        <v>139.1027278023139</v>
+        <v>138.811751497006</v>
       </c>
       <c r="FJ2" t="n">
-        <v>41.67212520660037</v>
+        <v>41.58495508982036</v>
       </c>
       <c r="FK2" t="n">
-        <v>14.0863521825128</v>
+        <v>14.05688622754491</v>
       </c>
       <c r="FL2" t="n">
-        <v>66.32324152599777</v>
+        <v>66.18450598802396</v>
       </c>
       <c r="FM2" t="n">
-        <v>1658.667969490883</v>
+        <v>1655.198353293413</v>
       </c>
       <c r="FN2" t="n">
-        <v>42.25905654753841</v>
+        <v>42.17065868263473</v>
       </c>
       <c r="FO2" t="n">
-        <v>35.80281179722004</v>
+        <v>35.72791916167665</v>
       </c>
       <c r="FP2" t="n">
-        <v>32.86815509252987</v>
+        <v>32.79940119760479</v>
       </c>
       <c r="FQ2" t="n">
-        <v>58.69313409380334</v>
+        <v>58.57035928143713</v>
       </c>
       <c r="FR2" t="n">
-        <v>7.043176091256401</v>
+        <v>7.028443113772455</v>
       </c>
       <c r="FS2" t="n">
-        <v>18.19487156907904</v>
+        <v>18.15681137724551</v>
       </c>
       <c r="FT2" t="n">
-        <v>53.99768336629907</v>
+        <v>53.88473053892216</v>
       </c>
       <c r="FU2" t="n">
-        <v>164.9277068035874</v>
+        <v>164.5827095808383</v>
       </c>
       <c r="FV2" t="n">
-        <v>1321.769379792451</v>
+        <v>1319.004491017964</v>
       </c>
       <c r="FW2" t="n">
-        <v>1059.998001734088</v>
+        <v>1057.780688622754</v>
       </c>
       <c r="FX2" t="n">
-        <v>234.7138432411195</v>
+        <v>234.222866766467</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.3606910699715129</v>
+        <v>0.359936573229745</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.7357532666500192</v>
+        <v>0.734214211517669</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.4499806947191589</v>
+        <v>0.4490394211576846</v>
       </c>
       <c r="GB2" t="n">
-        <v>1.170601952204189</v>
+        <v>1.168153276779774</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.1487805368330501</v>
+        <v>0.1484693164019818</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.3727763672554377</v>
+        <v>0.3719965903828787</v>
       </c>
       <c r="GE2" t="n">
-        <v>2.347138432411196</v>
+        <v>2.342228667664671</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.303383726934676</v>
+        <v>1.300657297429994</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.1540579724386632</v>
+        <v>0.1537357126215362</v>
       </c>
       <c r="GH2" t="n">
-        <v>1.383485996027506</v>
+        <v>1.380592007894208</v>
       </c>
       <c r="GI2" t="n">
-        <v>1.402515757860991</v>
+        <v>1.399581963105085</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.1806532291439792</v>
+        <v>0.1802753371357581</v>
       </c>
       <c r="GK2" t="n">
-        <v>-0.7461626520714235</v>
+        <v>-0.7014221556886229</v>
       </c>
       <c r="GL2" t="n">
-        <v>-14.20115086568943</v>
+        <v>-13.90157185628743</v>
       </c>
       <c r="GM2" t="n">
-        <v>-2.555096819934791</v>
+        <v>-2.466991017964071</v>
       </c>
       <c r="GN2" t="n">
-        <v>-1.584917269533349</v>
+        <v>-0.5416916167664567</v>
       </c>
       <c r="GO2" t="n">
-        <v>-17.40427628905086</v>
+        <v>-17.18435628742515</v>
       </c>
       <c r="GP2" t="n">
-        <v>2.56805393737412</v>
+        <v>2.68862275449102</v>
       </c>
       <c r="GQ2" t="n">
-        <v>-24.92514631370743</v>
+        <v>-24.55995508982036</v>
       </c>
       <c r="GR2" t="n">
-        <v>-77.45106845133273</v>
+        <v>-65.33188622754506</v>
       </c>
       <c r="GS2" t="n">
-        <v>-10.85360500718021</v>
+        <v>-10.59341317365269</v>
       </c>
       <c r="GT2" t="n">
-        <v>-23.43096725101832</v>
+        <v>-23.28839820359281</v>
       </c>
       <c r="GU2" t="n">
-        <v>-8.600306174980354</v>
+        <v>-8.398802395209575</v>
       </c>
       <c r="GV2" t="n">
-        <v>-12.06079695811995</v>
+        <v>-11.68293413173652</v>
       </c>
       <c r="GW2" t="n">
-        <v>-4.188135042132928</v>
+        <v>-4.157784431137724</v>
       </c>
       <c r="GX2" t="n">
-        <v>-0.5887850994842907</v>
+        <v>-0.4544161676646681</v>
       </c>
       <c r="GY2" t="n">
-        <v>-11.17206762944699</v>
+        <v>-10.82485029940119</v>
       </c>
       <c r="GZ2" t="n">
-        <v>-40.25758099186244</v>
+        <v>-39.23061377245509</v>
       </c>
       <c r="HA2" t="n">
-        <v>28.18919626809725</v>
+        <v>38.3386227544911</v>
       </c>
       <c r="HB2" t="n">
-        <v>111.5205087562431</v>
+        <v>120.14625748503</v>
       </c>
       <c r="HC2" t="n">
-        <v>-30.8163283162182</v>
+        <v>-29.20999251497</v>
       </c>
       <c r="HD2" t="n">
-        <v>0.0954425925904695</v>
+        <v>0.09869222977031561</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.1733898553057128</v>
+        <v>0.1799021013112189</v>
       </c>
       <c r="HF2" t="n">
-        <v>-0.1116054592674882</v>
+        <v>-0.1088132069194944</v>
       </c>
       <c r="HG2" t="n">
-        <v>-0.3008718548323162</v>
+        <v>-0.2936655854956751</v>
       </c>
       <c r="HH2" t="n">
-        <v>-0.07512596698611998</v>
+        <v>-0.07441184163757181</v>
       </c>
       <c r="HI2" t="n">
-        <v>-0.1297942745614939</v>
+        <v>-0.1276853380697913</v>
       </c>
       <c r="HJ2" t="n">
-        <v>-0.308163283162183</v>
+        <v>-0.2920999251497007</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.04722789784520853</v>
+        <v>0.05734243736614841</v>
       </c>
       <c r="HL2" t="n">
-        <v>-0.04054827394358489</v>
+        <v>-0.03960509385225949</v>
       </c>
       <c r="HM2" t="n">
-        <v>-0.009176267622746259</v>
+        <v>0.001235463793358038</v>
       </c>
       <c r="HN2" t="n">
-        <v>-0.05611772666965509</v>
+        <v>-0.04581887107937677</v>
       </c>
       <c r="HO2" t="n">
-        <v>-0.07769766064118006</v>
+        <v>-0.07675658151615239</v>
       </c>
     </row>
     <row r="3">
@@ -2413,97 +2413,97 @@
         <v>2.79940119760479</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.821149556091437</v>
+        <v>4.77245508982036</v>
       </c>
       <c r="BO3" t="n">
-        <v>32.30170202581263</v>
+        <v>31.97544910179641</v>
       </c>
       <c r="BP3" t="n">
-        <v>12.05287389022859</v>
+        <v>11.9311377245509</v>
       </c>
       <c r="BQ3" t="n">
-        <v>126.3141183695956</v>
+        <v>125.0383233532934</v>
       </c>
       <c r="BR3" t="n">
-        <v>30.8553571589852</v>
+        <v>30.5437125748503</v>
       </c>
       <c r="BS3" t="n">
-        <v>13.98133371266517</v>
+        <v>13.84011976047904</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.24726564969609</v>
+        <v>46.77005988023953</v>
       </c>
       <c r="BU3" t="n">
-        <v>1432.363533114766</v>
+        <v>1417.896407185629</v>
       </c>
       <c r="BV3" t="n">
-        <v>32.30170202581263</v>
+        <v>31.97544910179641</v>
       </c>
       <c r="BW3" t="n">
-        <v>20.24882813558404</v>
+        <v>20.04431137724551</v>
       </c>
       <c r="BX3" t="n">
-        <v>36.64073662629492</v>
+        <v>36.27065868263473</v>
       </c>
       <c r="BY3" t="n">
-        <v>50.13995538335094</v>
+        <v>49.63353293413174</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.339034600482293</v>
+        <v>4.295209580838324</v>
       </c>
       <c r="CA3" t="n">
-        <v>15.90979353510174</v>
+        <v>15.74910179640719</v>
       </c>
       <c r="CB3" t="n">
-        <v>47.24726564969609</v>
+        <v>46.77005988023953</v>
       </c>
       <c r="CC3" t="n">
-        <v>112.8148996125396</v>
+        <v>111.6754491017964</v>
       </c>
       <c r="CD3" t="n">
-        <v>1191.788170265803</v>
+        <v>1179.750898203593</v>
       </c>
       <c r="CE3" t="n">
-        <v>976.282785108516</v>
+        <v>966.4221556886229</v>
       </c>
       <c r="CF3" t="n">
-        <v>197.2332283397007</v>
+        <v>195.241137724551</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.3294283388904916</v>
+        <v>0.3261010541941328</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.8950836566767367</v>
+        <v>0.8860431528668584</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.305339471885791</v>
+        <v>0.3022554890219561</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.9803004097385921</v>
+        <v>0.9703992015968064</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.09393370323261886</v>
+        <v>0.09298495615672719</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.2300080134252876</v>
+        <v>0.2276848916632456</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.972332283397007</v>
+        <v>1.952411377245509</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.357755740272518</v>
+        <v>1.344042166293978</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1182764334795006</v>
+        <v>0.1170818205072783</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.268308090971136</v>
+        <v>1.255497954127508</v>
       </c>
       <c r="CQ3" t="n">
-        <v>1.245660608948328</v>
+        <v>1.23307921569306</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.122182486372463</v>
+        <v>0.1209484215726969</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
@@ -2701,190 +2701,190 @@
         <v>2.058383233532934</v>
       </c>
       <c r="FF3" t="n">
-        <v>2.789895322477218</v>
+        <v>2.767964071856288</v>
       </c>
       <c r="FG3" t="n">
-        <v>23.43512070880863</v>
+        <v>23.25089820359282</v>
       </c>
       <c r="FH3" t="n">
-        <v>6.13776970944988</v>
+        <v>6.089520958083833</v>
       </c>
       <c r="FI3" t="n">
-        <v>114.9436872860614</v>
+        <v>114.0401197604791</v>
       </c>
       <c r="FJ3" t="n">
-        <v>32.36278574073572</v>
+        <v>32.10838323353293</v>
       </c>
       <c r="FK3" t="n">
-        <v>11.71756035440431</v>
+        <v>11.62544910179641</v>
       </c>
       <c r="FL3" t="n">
-        <v>33.47874386972661</v>
+        <v>33.21556886227545</v>
       </c>
       <c r="FM3" t="n">
-        <v>1478.08654184843</v>
+        <v>1466.467365269461</v>
       </c>
       <c r="FN3" t="n">
-        <v>54.68194832055347</v>
+        <v>54.25209580838325</v>
       </c>
       <c r="FO3" t="n">
-        <v>25.10905790229496</v>
+        <v>24.91167664670659</v>
       </c>
       <c r="FP3" t="n">
-        <v>37.38459732119472</v>
+        <v>37.09071856287426</v>
       </c>
       <c r="FQ3" t="n">
-        <v>77.00111090037122</v>
+        <v>76.39580838323354</v>
       </c>
       <c r="FR3" t="n">
-        <v>2.231916257981774</v>
+        <v>2.21437125748503</v>
       </c>
       <c r="FS3" t="n">
-        <v>23.99309977330407</v>
+        <v>23.80449101796407</v>
       </c>
       <c r="FT3" t="n">
-        <v>45.19630422413093</v>
+        <v>44.84101796407186</v>
       </c>
       <c r="FU3" t="n">
-        <v>167.3937193486331</v>
+        <v>166.0778443113772</v>
       </c>
       <c r="FV3" t="n">
-        <v>1182.91561673034</v>
+        <v>1173.616766467066</v>
       </c>
       <c r="FW3" t="n">
-        <v>947.4484515132632</v>
+        <v>940.0005988023953</v>
       </c>
       <c r="FX3" t="n">
-        <v>221.7408802304892</v>
+        <v>219.9977844311377</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.3176729547862714</v>
+        <v>0.3151757409550647</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.8331914275390645</v>
+        <v>0.8266417445221602</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1301951150489368</v>
+        <v>0.1291716566866268</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.6182053762187614</v>
+        <v>0.6133456895732347</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.07740525997470617</v>
+        <v>0.07679678045857286</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.4031761000767671</v>
+        <v>0.4000067495911361</v>
       </c>
       <c r="GE3" t="n">
-        <v>2.217408802304893</v>
+        <v>2.199977844311377</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.558412590267433</v>
+        <v>1.546161973976345</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.1319606677465341</v>
+        <v>0.1309233304481996</v>
       </c>
       <c r="GH3" t="n">
-        <v>1.148066263964743</v>
+        <v>1.139041363008212</v>
       </c>
       <c r="GI3" t="n">
-        <v>1.192382915373859</v>
+        <v>1.183009643071313</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.1039722096075241</v>
+        <v>0.1031548884097919</v>
       </c>
       <c r="GK3" t="n">
-        <v>2.031254233614219</v>
+        <v>2.004491017964072</v>
       </c>
       <c r="GL3" t="n">
-        <v>8.866581317004002</v>
+        <v>8.724550898203592</v>
       </c>
       <c r="GM3" t="n">
-        <v>5.915104180778713</v>
+        <v>5.841616766467068</v>
       </c>
       <c r="GN3" t="n">
-        <v>11.37043108353427</v>
+        <v>10.99820359281436</v>
       </c>
       <c r="GO3" t="n">
-        <v>-1.507428581750524</v>
+        <v>-1.56467065868263</v>
       </c>
       <c r="GP3" t="n">
-        <v>2.263773358260853</v>
+        <v>2.214670658682634</v>
       </c>
       <c r="GQ3" t="n">
-        <v>13.76852177996948</v>
+        <v>13.55449101796408</v>
       </c>
       <c r="GR3" t="n">
-        <v>-45.72300873366385</v>
+        <v>-48.57095808383224</v>
       </c>
       <c r="GS3" t="n">
-        <v>-22.38024629474084</v>
+        <v>-22.27664670658683</v>
       </c>
       <c r="GT3" t="n">
-        <v>-4.860229766710923</v>
+        <v>-4.867365269461075</v>
       </c>
       <c r="GU3" t="n">
-        <v>-0.7438606948998014</v>
+        <v>-0.8200598802395263</v>
       </c>
       <c r="GV3" t="n">
-        <v>-26.86115551702027</v>
+        <v>-26.7622754491018</v>
       </c>
       <c r="GW3" t="n">
-        <v>2.107118342500519</v>
+        <v>2.080838323353294</v>
       </c>
       <c r="GX3" t="n">
-        <v>-8.083306238202333</v>
+        <v>-8.055389221556885</v>
       </c>
       <c r="GY3" t="n">
-        <v>2.050961425565163</v>
+        <v>1.92904191616767</v>
       </c>
       <c r="GZ3" t="n">
-        <v>-54.57881973609344</v>
+        <v>-54.40239520958083</v>
       </c>
       <c r="HA3" t="n">
-        <v>8.872553535462885</v>
+        <v>6.134131736527024</v>
       </c>
       <c r="HB3" t="n">
-        <v>28.83433359525282</v>
+        <v>26.42155688622756</v>
       </c>
       <c r="HC3" t="n">
-        <v>-24.50765189078854</v>
+        <v>-24.75664670658676</v>
       </c>
       <c r="HD3" t="n">
-        <v>0.01175538410422017</v>
+        <v>0.01092531323906815</v>
       </c>
       <c r="HE3" t="n">
-        <v>0.06189222913767223</v>
+        <v>0.0594014083446982</v>
       </c>
       <c r="HF3" t="n">
-        <v>0.1751443568368541</v>
+        <v>0.1730838323353293</v>
       </c>
       <c r="HG3" t="n">
-        <v>0.3620950335198307</v>
+        <v>0.3570535120235717</v>
       </c>
       <c r="HH3" t="n">
-        <v>0.01652844325791269</v>
+        <v>0.01618817569815434</v>
       </c>
       <c r="HI3" t="n">
-        <v>-0.1731680866514796</v>
+        <v>-0.1723218579278906</v>
       </c>
       <c r="HJ3" t="n">
-        <v>-0.2450765189078856</v>
+        <v>-0.2475664670658679</v>
       </c>
       <c r="HK3" t="n">
-        <v>-0.2006568499949155</v>
+        <v>-0.2021198076823671</v>
       </c>
       <c r="HL3" t="n">
-        <v>-0.01368423426703352</v>
+        <v>-0.01384150994092137</v>
       </c>
       <c r="HM3" t="n">
-        <v>0.1202418270063925</v>
+        <v>0.1164565911192952</v>
       </c>
       <c r="HN3" t="n">
-        <v>0.05327769357446832</v>
+        <v>0.05006957262174727</v>
       </c>
       <c r="HO3" t="n">
-        <v>0.01821027676493889</v>
+        <v>0.017793533162905</v>
       </c>
     </row>
     <row r="4">
@@ -3084,97 +3084,97 @@
         <v>3.008982035928144</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.004276514843617</v>
+        <v>3.032634730538922</v>
       </c>
       <c r="BO4" t="n">
-        <v>24.03421211874893</v>
+        <v>24.26107784431138</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.296100107477355</v>
+        <v>7.364970059880239</v>
       </c>
       <c r="BQ4" t="n">
-        <v>124.4628841863784</v>
+        <v>125.6377245508982</v>
       </c>
       <c r="BR4" t="n">
-        <v>27.46767099285593</v>
+        <v>27.72694610778443</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.72955898158435</v>
+        <v>10.83083832335329</v>
       </c>
       <c r="BT4" t="n">
-        <v>43.34741828560076</v>
+        <v>43.7565868263473</v>
       </c>
       <c r="BU4" t="n">
-        <v>1493.125427877278</v>
+        <v>1507.219461077844</v>
       </c>
       <c r="BV4" t="n">
-        <v>38.62641233370365</v>
+        <v>38.99101796407186</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.87547077790122</v>
+        <v>12.99700598802395</v>
       </c>
       <c r="BX4" t="n">
-        <v>23.17584740022219</v>
+        <v>23.39461077844312</v>
       </c>
       <c r="BY4" t="n">
-        <v>38.19722997444028</v>
+        <v>38.55778443113773</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.433458874106991</v>
+        <v>3.465868263473054</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.154464826004103</v>
+        <v>8.231437125748503</v>
       </c>
       <c r="CB4" t="n">
-        <v>37.7680476151769</v>
+        <v>38.12455089820359</v>
       </c>
       <c r="CC4" t="n">
-        <v>75.10691287109043</v>
+        <v>75.81586826347305</v>
       </c>
       <c r="CD4" t="n">
-        <v>1259.221042078739</v>
+        <v>1271.107185628742</v>
       </c>
       <c r="CE4" t="n">
-        <v>1090.981557247496</v>
+        <v>1101.279640718563</v>
       </c>
       <c r="CF4" t="n">
-        <v>185.3638609658512</v>
+        <v>187.1135628742515</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.3260051860263203</v>
+        <v>0.3290824411782496</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.7465171945975048</v>
+        <v>0.7535637815278533</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.4399119182449582</v>
+        <v>0.444064371257485</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.5710509724643223</v>
+        <v>0.5764412840984696</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.07473579280488347</v>
+        <v>0.07544124509000072</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.1328155238831431</v>
+        <v>0.1340692071760603</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.853638609658512</v>
+        <v>1.871135628742515</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.111321405983214</v>
+        <v>1.121811483039028</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1265659357193958</v>
+        <v>0.1277606273821223</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.241293523698978</v>
+        <v>1.253010444332721</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.215988002676357</v>
+        <v>1.227466057340241</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.09355141375500503</v>
+        <v>0.09443447200771826</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -3372,190 +3372,190 @@
         <v>1.833832335329341</v>
       </c>
       <c r="FF4" t="n">
-        <v>5.56000623188013</v>
+        <v>5.510479041916168</v>
       </c>
       <c r="FG4" t="n">
-        <v>35.21337280190749</v>
+        <v>34.8997005988024</v>
       </c>
       <c r="FH4" t="n">
-        <v>14.82668328501368</v>
+        <v>14.69461077844311</v>
       </c>
       <c r="FI4" t="n">
-        <v>137.1468203863765</v>
+        <v>135.9251497005988</v>
       </c>
       <c r="FJ4" t="n">
-        <v>39.53782209336981</v>
+        <v>39.18562874251498</v>
       </c>
       <c r="FK4" t="n">
-        <v>9.884455523342453</v>
+        <v>9.796407185628745</v>
       </c>
       <c r="FL4" t="n">
-        <v>64.24896090172595</v>
+        <v>63.67664670658684</v>
       </c>
       <c r="FM4" t="n">
-        <v>1640.201838404638</v>
+        <v>1625.59131736527</v>
       </c>
       <c r="FN4" t="n">
-        <v>43.86227138483213</v>
+        <v>43.47155688622755</v>
       </c>
       <c r="FO4" t="n">
-        <v>23.47558186793832</v>
+        <v>23.26646706586826</v>
       </c>
       <c r="FP4" t="n">
-        <v>38.302265152952</v>
+        <v>37.96107784431138</v>
       </c>
       <c r="FQ4" t="n">
-        <v>73.5156379548595</v>
+        <v>72.86077844311379</v>
       </c>
       <c r="FR4" t="n">
-        <v>3.088892351044517</v>
+        <v>3.061377245508982</v>
       </c>
       <c r="FS4" t="n">
-        <v>25.32891727856503</v>
+        <v>25.10329341317365</v>
       </c>
       <c r="FT4" t="n">
-        <v>61.77784702089033</v>
+        <v>61.22754491017965</v>
       </c>
       <c r="FU4" t="n">
-        <v>213.7513506922805</v>
+        <v>211.8473053892216</v>
       </c>
       <c r="FV4" t="n">
-        <v>1333.165938710813</v>
+        <v>1321.290419161677</v>
       </c>
       <c r="FW4" t="n">
-        <v>1040.956722302002</v>
+        <v>1031.684131736527</v>
       </c>
       <c r="FX4" t="n">
-        <v>238.0300445714904</v>
+        <v>235.9097305389221</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.5508524692696054</v>
+        <v>0.5459456087824351</v>
       </c>
       <c r="FZ4" t="n">
-        <v>1.309347146581648</v>
+        <v>1.29768379906853</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.7680983930133141</v>
+        <v>0.7612563584120471</v>
       </c>
       <c r="GB4" t="n">
-        <v>1.206694363204917</v>
+        <v>1.195945421843626</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.1490286697634714</v>
+        <v>0.1477011584389101</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.5204560914494611</v>
+        <v>0.5158199945398355</v>
       </c>
       <c r="GE4" t="n">
-        <v>2.380300445714905</v>
+        <v>2.359097305389222</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.494817326212268</v>
+        <v>1.481501855223722</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.1287808332280758</v>
+        <v>0.1276336847312931</v>
       </c>
       <c r="GH4" t="n">
-        <v>1.370397250155551</v>
+        <v>1.35819008309423</v>
       </c>
       <c r="GI4" t="n">
-        <v>1.393547976026481</v>
+        <v>1.381134587901695</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.1720699633657759</v>
+        <v>0.1705372057739149</v>
       </c>
       <c r="GK4" t="n">
-        <v>-2.555729717036513</v>
+        <v>-2.477844311377246</v>
       </c>
       <c r="GL4" t="n">
-        <v>-11.17916068315856</v>
+        <v>-10.63862275449102</v>
       </c>
       <c r="GM4" t="n">
-        <v>-7.530583177536324</v>
+        <v>-7.329640718562874</v>
       </c>
       <c r="GN4" t="n">
-        <v>-12.68393619999812</v>
+        <v>-10.28742514970061</v>
       </c>
       <c r="GO4" t="n">
-        <v>-12.07015110051388</v>
+        <v>-11.45868263473055</v>
       </c>
       <c r="GP4" t="n">
-        <v>0.8451034582418941</v>
+        <v>1.03443113772455</v>
       </c>
       <c r="GQ4" t="n">
-        <v>-20.90154261612519</v>
+        <v>-19.92005988023953</v>
       </c>
       <c r="GR4" t="n">
-        <v>-147.0764105273606</v>
+        <v>-118.3718562874253</v>
       </c>
       <c r="GS4" t="n">
-        <v>-5.235859051128486</v>
+        <v>-4.480538922155688</v>
       </c>
       <c r="GT4" t="n">
-        <v>-10.60011109003711</v>
+        <v>-10.26946107784431</v>
       </c>
       <c r="GU4" t="n">
-        <v>-15.12641775272981</v>
+        <v>-14.56646706586827</v>
       </c>
       <c r="GV4" t="n">
-        <v>-35.31840798041922</v>
+        <v>-34.30299401197606</v>
       </c>
       <c r="GW4" t="n">
-        <v>0.3445665230624746</v>
+        <v>0.4044910179640717</v>
       </c>
       <c r="GX4" t="n">
-        <v>-17.17445245256093</v>
+        <v>-16.87185628742515</v>
       </c>
       <c r="GY4" t="n">
-        <v>-24.00979940571343</v>
+        <v>-23.10299401197605</v>
       </c>
       <c r="GZ4" t="n">
-        <v>-138.6444378211901</v>
+        <v>-136.0314371257485</v>
       </c>
       <c r="HA4" t="n">
-        <v>-73.94489663207469</v>
+        <v>-50.18323353293431</v>
       </c>
       <c r="HB4" t="n">
-        <v>50.02483494549415</v>
+        <v>69.59550898203588</v>
       </c>
       <c r="HC4" t="n">
-        <v>-52.66618360563925</v>
+        <v>-48.79616766467063</v>
       </c>
       <c r="HD4" t="n">
-        <v>-0.2248472832432851</v>
+        <v>-0.2168631676041856</v>
       </c>
       <c r="HE4" t="n">
-        <v>-0.562829951984143</v>
+        <v>-0.5441200175406764</v>
       </c>
       <c r="HF4" t="n">
-        <v>-0.3281864747683559</v>
+        <v>-0.3171919871545621</v>
       </c>
       <c r="HG4" t="n">
-        <v>-0.6356433907405942</v>
+        <v>-0.619504137745156</v>
       </c>
       <c r="HH4" t="n">
-        <v>-0.0742928769585879</v>
+        <v>-0.07225991334890938</v>
       </c>
       <c r="HI4" t="n">
-        <v>-0.387640567566318</v>
+        <v>-0.3817507873637752</v>
       </c>
       <c r="HJ4" t="n">
-        <v>-0.5266618360563931</v>
+        <v>-0.4879616766467072</v>
       </c>
       <c r="HK4" t="n">
-        <v>-0.3834959202290542</v>
+        <v>-0.359690372184694</v>
       </c>
       <c r="HL4" t="n">
-        <v>-0.002214897508680036</v>
+        <v>0.0001269426508292704</v>
       </c>
       <c r="HM4" t="n">
-        <v>-0.1291037264565729</v>
+        <v>-0.1051796387615089</v>
       </c>
       <c r="HN4" t="n">
-        <v>-0.1775599733501247</v>
+        <v>-0.1536685305614538</v>
       </c>
       <c r="HO4" t="n">
-        <v>-0.0785185496107709</v>
+        <v>-0.07610273376619667</v>
       </c>
     </row>
     <row r="5">
@@ -3755,97 +3755,97 @@
         <v>2.290419161676647</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.235944400791178</v>
+        <v>2.24311377245509</v>
       </c>
       <c r="BO5" t="n">
-        <v>26.83133280949414</v>
+        <v>26.91736526946108</v>
       </c>
       <c r="BP5" t="n">
-        <v>11.17972200395589</v>
+        <v>11.21556886227545</v>
       </c>
       <c r="BQ5" t="n">
-        <v>134.7156501476685</v>
+        <v>135.1476047904192</v>
       </c>
       <c r="BR5" t="n">
-        <v>38.01105481345002</v>
+        <v>38.13293413173653</v>
       </c>
       <c r="BS5" t="n">
-        <v>14.53363860514266</v>
+        <v>14.58023952095808</v>
       </c>
       <c r="BT5" t="n">
-        <v>45.83686021621914</v>
+        <v>45.98383233532933</v>
       </c>
       <c r="BU5" t="n">
-        <v>1580.812691359363</v>
+        <v>1585.881437125749</v>
       </c>
       <c r="BV5" t="n">
-        <v>48.07280461701033</v>
+        <v>48.22694610778443</v>
       </c>
       <c r="BW5" t="n">
-        <v>23.47741620830737</v>
+        <v>23.55269461077844</v>
       </c>
       <c r="BX5" t="n">
-        <v>32.98017991166988</v>
+        <v>33.08592814371258</v>
       </c>
       <c r="BY5" t="n">
-        <v>67.07833202373534</v>
+        <v>67.2934131736527</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.912902701384561</v>
+        <v>3.925449101796407</v>
       </c>
       <c r="CA5" t="n">
-        <v>17.88755520632942</v>
+        <v>17.94491017964072</v>
       </c>
       <c r="CB5" t="n">
-        <v>47.51381851681253</v>
+        <v>47.66616766467066</v>
       </c>
       <c r="CC5" t="n">
-        <v>178.8755520632942</v>
+        <v>179.4491017964072</v>
       </c>
       <c r="CD5" t="n">
-        <v>1311.940377164223</v>
+        <v>1316.147005988024</v>
       </c>
       <c r="CE5" t="n">
-        <v>1064.868520876799</v>
+        <v>1068.282934131737</v>
       </c>
       <c r="CF5" t="n">
-        <v>224.5447164494541</v>
+        <v>225.2647005988024</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.281711248909206</v>
+        <v>0.2826145328390837</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.157899778981146</v>
+        <v>1.1616124893071</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.4082594910373178</v>
+        <v>0.4095685414884517</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.141160909497201</v>
+        <v>1.144819948016056</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.09583004818648823</v>
+        <v>0.09613731934751371</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.3922195414332107</v>
+        <v>0.3934771611063066</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.24544716449454</v>
+        <v>2.252647005988023</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.381141582326317</v>
+        <v>1.385570099118003</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1451495895292898</v>
+        <v>0.1456149997397725</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.350650776366131</v>
+        <v>1.354981526898431</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.345842674266909</v>
+        <v>1.350158008015619</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1257944918916831</v>
+        <v>0.1261978415748529</v>
       </c>
       <c r="CS5" t="n">
         <v>1</v>
@@ -4043,190 +4043,190 @@
         <v>3.375748502994012</v>
       </c>
       <c r="FF5" t="n">
-        <v>4.692674379747293</v>
+        <v>4.71377245508982</v>
       </c>
       <c r="FG5" t="n">
-        <v>28.15604627848375</v>
+        <v>28.28263473053892</v>
       </c>
       <c r="FH5" t="n">
-        <v>9.971933056962996</v>
+        <v>10.01676646706587</v>
       </c>
       <c r="FI5" t="n">
-        <v>159.5509289114079</v>
+        <v>160.2682634730539</v>
       </c>
       <c r="FJ5" t="n">
-        <v>33.43530495569946</v>
+        <v>33.58562874251497</v>
       </c>
       <c r="FK5" t="n">
-        <v>12.31827024683664</v>
+        <v>12.37365269461078</v>
       </c>
       <c r="FL5" t="n">
-        <v>42.23406941772564</v>
+        <v>42.42395209580838</v>
       </c>
       <c r="FM5" t="n">
-        <v>1912.264809747022</v>
+        <v>1920.862275449102</v>
       </c>
       <c r="FN5" t="n">
-        <v>45.7535752025361</v>
+        <v>45.95928143712575</v>
       </c>
       <c r="FO5" t="n">
-        <v>28.15604627848375</v>
+        <v>28.28263473053892</v>
       </c>
       <c r="FP5" t="n">
-        <v>29.32921487342058</v>
+        <v>29.46107784431138</v>
       </c>
       <c r="FQ5" t="n">
-        <v>67.45719420886732</v>
+        <v>67.76047904191616</v>
       </c>
       <c r="FR5" t="n">
-        <v>5.279258677215704</v>
+        <v>5.302994011976048</v>
       </c>
       <c r="FS5" t="n">
-        <v>21.11703470886282</v>
+        <v>21.21197604790419</v>
       </c>
       <c r="FT5" t="n">
-        <v>55.72550825949909</v>
+        <v>55.97604790419161</v>
       </c>
       <c r="FU5" t="n">
-        <v>153.6850859367238</v>
+        <v>154.3760479041916</v>
       </c>
       <c r="FV5" t="n">
-        <v>1591.989783329269</v>
+        <v>1599.147305389221</v>
       </c>
       <c r="FW5" t="n">
-        <v>1325.68051227861</v>
+        <v>1331.640718562874</v>
       </c>
       <c r="FX5" t="n">
-        <v>242.9632160114161</v>
+        <v>244.0555688622754</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.388663371924</v>
+        <v>0.3904107868179724</v>
       </c>
       <c r="FZ5" t="n">
-        <v>1.08634318027658</v>
+        <v>1.091227335538713</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.3627551615003701</v>
+        <v>0.3643860941219166</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.9114188579203186</v>
+        <v>0.9155165604619636</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.07886866196709066</v>
+        <v>0.07922325230038278</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.3009281329393768</v>
+        <v>0.3022810937262667</v>
       </c>
       <c r="GE5" t="n">
-        <v>2.429632160114161</v>
+        <v>2.440555688622754</v>
       </c>
       <c r="GF5" t="n">
-        <v>1.692318352967214</v>
+        <v>1.699926948242552</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.1681846449219795</v>
+        <v>0.1689407963236907</v>
       </c>
       <c r="GH5" t="n">
-        <v>1.59794608884707</v>
+        <v>1.605130390217157</v>
       </c>
       <c r="GI5" t="n">
-        <v>1.564950563199453</v>
+        <v>1.571986518012813</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.1025494767173756</v>
+        <v>0.1030105350416986</v>
       </c>
       <c r="GK5" t="n">
-        <v>-2.456729978956115</v>
+        <v>-2.47065868263473</v>
       </c>
       <c r="GL5" t="n">
-        <v>-1.324713468989618</v>
+        <v>-1.365269461077844</v>
       </c>
       <c r="GM5" t="n">
-        <v>1.207788946992894</v>
+        <v>1.198802395209581</v>
       </c>
       <c r="GN5" t="n">
-        <v>-24.83527876373947</v>
+        <v>-25.12065868263471</v>
       </c>
       <c r="GO5" t="n">
-        <v>4.575749857750566</v>
+        <v>4.547305389221556</v>
       </c>
       <c r="GP5" t="n">
-        <v>2.215368358306014</v>
+        <v>2.206586826347307</v>
       </c>
       <c r="GQ5" t="n">
-        <v>3.602790798493508</v>
+        <v>3.55988023952095</v>
       </c>
       <c r="GR5" t="n">
-        <v>-331.4521183876589</v>
+        <v>-334.9808383233531</v>
       </c>
       <c r="GS5" t="n">
-        <v>2.319229414474229</v>
+        <v>2.267664670658682</v>
       </c>
       <c r="GT5" t="n">
-        <v>-4.678630070176382</v>
+        <v>-4.729940119760478</v>
       </c>
       <c r="GU5" t="n">
-        <v>3.650965038249304</v>
+        <v>3.624850299401203</v>
       </c>
       <c r="GV5" t="n">
-        <v>-0.3788621851319789</v>
+        <v>-0.467065868263461</v>
       </c>
       <c r="GW5" t="n">
-        <v>-1.366355975831143</v>
+        <v>-1.377544910179641</v>
       </c>
       <c r="GX5" t="n">
-        <v>-3.229479502533394</v>
+        <v>-3.267065868263472</v>
       </c>
       <c r="GY5" t="n">
-        <v>-8.211689742686559</v>
+        <v>-8.30988023952095</v>
       </c>
       <c r="GZ5" t="n">
-        <v>25.19046612657041</v>
+        <v>25.07305389221557</v>
       </c>
       <c r="HA5" t="n">
-        <v>-280.0494061650454</v>
+        <v>-283.0002994011973</v>
       </c>
       <c r="HB5" t="n">
-        <v>-260.8119914018116</v>
+        <v>-263.3577844311376</v>
       </c>
       <c r="HC5" t="n">
-        <v>-18.41849956196202</v>
+        <v>-18.79086826347304</v>
       </c>
       <c r="HD5" t="n">
-        <v>-0.106952123014794</v>
+        <v>-0.1077962539788887</v>
       </c>
       <c r="HE5" t="n">
-        <v>0.07155659870456521</v>
+        <v>0.0703851537683875</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.04550432953694772</v>
+        <v>0.04518244736653509</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.2297420515768824</v>
+        <v>0.2293033875540923</v>
       </c>
       <c r="HH5" t="n">
-        <v>0.01696138621939756</v>
+        <v>0.01691406704713093</v>
       </c>
       <c r="HI5" t="n">
-        <v>0.09129140849383388</v>
+        <v>0.09119606738003994</v>
       </c>
       <c r="HJ5" t="n">
-        <v>-0.1841849956196207</v>
+        <v>-0.1879086826347307</v>
       </c>
       <c r="HK5" t="n">
-        <v>-0.311176770640897</v>
+        <v>-0.3143568491245485</v>
       </c>
       <c r="HL5" t="n">
-        <v>-0.02303505539268969</v>
+        <v>-0.02332579658391823</v>
       </c>
       <c r="HM5" t="n">
-        <v>-0.2472953124809394</v>
+        <v>-0.2501488633187265</v>
       </c>
       <c r="HN5" t="n">
-        <v>-0.2191078889325435</v>
+        <v>-0.2218285099971937</v>
       </c>
       <c r="HO5" t="n">
-        <v>0.02324501517430755</v>
+        <v>0.0231873065331543</v>
       </c>
     </row>
     <row r="6">
@@ -4426,97 +4426,97 @@
         <v>3.630239520958084</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.623200657508512</v>
+        <v>6.581736526946108</v>
       </c>
       <c r="BO6" t="n">
-        <v>43.30554276063258</v>
+        <v>43.03443113772455</v>
       </c>
       <c r="BP6" t="n">
-        <v>12.22744736770802</v>
+        <v>12.15089820359282</v>
       </c>
       <c r="BQ6" t="n">
-        <v>153.8620460436593</v>
+        <v>152.8988023952096</v>
       </c>
       <c r="BR6" t="n">
-        <v>32.09704934023356</v>
+        <v>31.89610778443114</v>
       </c>
       <c r="BS6" t="n">
-        <v>17.83169407790753</v>
+        <v>17.72005988023952</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.0424671019951</v>
+        <v>55.69161676646707</v>
       </c>
       <c r="BU6" t="n">
-        <v>1724.579555820486</v>
+        <v>1713.782934131737</v>
       </c>
       <c r="BV6" t="n">
-        <v>35.66338815581506</v>
+        <v>35.44011976047904</v>
       </c>
       <c r="BW6" t="n">
-        <v>27.51175657734305</v>
+        <v>27.33952095808383</v>
       </c>
       <c r="BX6" t="n">
-        <v>42.28658881332358</v>
+        <v>42.02185628742515</v>
       </c>
       <c r="BY6" t="n">
-        <v>51.96665131275909</v>
+        <v>51.64131736526946</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.075815789236008</v>
+        <v>4.050299401197605</v>
       </c>
       <c r="CA6" t="n">
-        <v>17.32221710425303</v>
+        <v>17.21377245508982</v>
       </c>
       <c r="CB6" t="n">
-        <v>46.36240460255959</v>
+        <v>46.07215568862276</v>
       </c>
       <c r="CC6" t="n">
-        <v>142.6535526232603</v>
+        <v>141.7604790419162</v>
       </c>
       <c r="CD6" t="n">
-        <v>1455.575713730909</v>
+        <v>1446.463173652695</v>
       </c>
       <c r="CE6" t="n">
-        <v>1200.837226903659</v>
+        <v>1193.319461077844</v>
       </c>
       <c r="CF6" t="n">
-        <v>209.4459838693653</v>
+        <v>208.1347604790419</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.4120769639852581</v>
+        <v>0.4094971821063755</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.7743717008062365</v>
+        <v>0.7695237955461627</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.373616447346634</v>
+        <v>0.3712774451097804</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.7019460525906457</v>
+        <v>0.6975515635395875</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.09911685725458515</v>
+        <v>0.09849634241249287</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.2552668677244284</v>
+        <v>0.2536687855767008</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.094459838693653</v>
+        <v>2.081347604790419</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.479911944798523</v>
+        <v>1.470647049278496</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1772201484777829</v>
+        <v>0.1761106729002249</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.535019114492183</v>
+        <v>1.525409224007145</v>
       </c>
       <c r="CQ6" t="n">
-        <v>1.468226342811463</v>
+        <v>1.459034604266673</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1300212126031494</v>
+        <v>0.1292072229908692</v>
       </c>
       <c r="CS6" t="n">
         <v>1</v>
@@ -4714,190 +4714,190 @@
         <v>2.664670658682635</v>
       </c>
       <c r="FF6" t="n">
-        <v>5.995764127852891</v>
+        <v>5.994011976047903</v>
       </c>
       <c r="FG6" t="n">
-        <v>32.9767027031909</v>
+        <v>32.96706586826347</v>
       </c>
       <c r="FH6" t="n">
-        <v>14.38983390684694</v>
+        <v>14.38562874251497</v>
       </c>
       <c r="FI6" t="n">
-        <v>119.3157061442725</v>
+        <v>119.2808383233533</v>
       </c>
       <c r="FJ6" t="n">
-        <v>34.77543194154677</v>
+        <v>34.76526946107784</v>
       </c>
       <c r="FK6" t="n">
-        <v>11.99152825570578</v>
+        <v>11.98802395209581</v>
       </c>
       <c r="FL6" t="n">
-        <v>37.17373759268793</v>
+        <v>37.162874251497</v>
       </c>
       <c r="FM6" t="n">
-        <v>1554.102061939469</v>
+        <v>1553.647904191617</v>
       </c>
       <c r="FN6" t="n">
-        <v>50.96399508674958</v>
+        <v>50.94910179640718</v>
       </c>
       <c r="FO6" t="n">
-        <v>19.18644520912925</v>
+        <v>19.18083832335329</v>
       </c>
       <c r="FP6" t="n">
-        <v>32.37712629040561</v>
+        <v>32.36766467065868</v>
       </c>
       <c r="FQ6" t="n">
-        <v>94.13349680729038</v>
+        <v>94.10598802395208</v>
       </c>
       <c r="FR6" t="n">
-        <v>4.796611302282313</v>
+        <v>4.795209580838323</v>
       </c>
       <c r="FS6" t="n">
-        <v>24.58263292419685</v>
+        <v>24.5754491017964</v>
       </c>
       <c r="FT6" t="n">
-        <v>41.37077248218495</v>
+        <v>41.35868263473053</v>
       </c>
       <c r="FU6" t="n">
-        <v>173.2775832949486</v>
+        <v>173.2269461077844</v>
       </c>
       <c r="FV6" t="n">
-        <v>1188.960026553228</v>
+        <v>1188.612574850299</v>
       </c>
       <c r="FW6" t="n">
-        <v>949.1294614391128</v>
+        <v>948.8520958083832</v>
       </c>
       <c r="FX6" t="n">
-        <v>238.391581723431</v>
+        <v>238.3219161676647</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.570607436782943</v>
+        <v>0.5704406872529449</v>
       </c>
       <c r="FZ6" t="n">
-        <v>1.332181016099562</v>
+        <v>1.331791710696254</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.4436259821870952</v>
+        <v>0.4434963406520291</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.7940194627357631</v>
+        <v>0.7937874251497005</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0955907231576669</v>
+        <v>0.09556278852672591</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.4409869552207112</v>
+        <v>0.4408580848927447</v>
       </c>
       <c r="GE6" t="n">
-        <v>2.383915817234309</v>
+        <v>2.383219161676646</v>
       </c>
       <c r="GF6" t="n">
-        <v>1.518707287329771</v>
+        <v>1.518263473053892</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.1157814546740208</v>
+        <v>0.1157476196730993</v>
       </c>
       <c r="GH6" t="n">
-        <v>1.189110977416148</v>
+        <v>1.188763481600605</v>
       </c>
       <c r="GI6" t="n">
-        <v>1.249383705673712</v>
+        <v>1.249018596261744</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.126810000208486</v>
+        <v>0.1267729423179457</v>
       </c>
       <c r="GK6" t="n">
-        <v>0.627436529655621</v>
+        <v>0.587724550898205</v>
       </c>
       <c r="GL6" t="n">
-        <v>10.32884005744167</v>
+        <v>10.06736526946109</v>
       </c>
       <c r="GM6" t="n">
-        <v>-2.162386539138916</v>
+        <v>-2.234730538922152</v>
       </c>
       <c r="GN6" t="n">
-        <v>34.54633989938677</v>
+        <v>33.61796407185631</v>
       </c>
       <c r="GO6" t="n">
-        <v>-2.67838260131321</v>
+        <v>-2.869161676646698</v>
       </c>
       <c r="GP6" t="n">
-        <v>5.840165822201749</v>
+        <v>5.732035928143715</v>
       </c>
       <c r="GQ6" t="n">
-        <v>18.86872950930717</v>
+        <v>18.52874251497007</v>
       </c>
       <c r="GR6" t="n">
-        <v>170.4774938810162</v>
+        <v>160.1350299401199</v>
       </c>
       <c r="GS6" t="n">
-        <v>-15.30060693093451</v>
+        <v>-15.50898203592813</v>
       </c>
       <c r="GT6" t="n">
-        <v>8.3253113682138</v>
+        <v>8.158682634730543</v>
       </c>
       <c r="GU6" t="n">
-        <v>9.90946252291797</v>
+        <v>9.654191616766468</v>
       </c>
       <c r="GV6" t="n">
-        <v>-42.16684549453129</v>
+        <v>-42.46467065868262</v>
       </c>
       <c r="GW6" t="n">
-        <v>-0.7207955130463057</v>
+        <v>-0.7449101796407183</v>
       </c>
       <c r="GX6" t="n">
-        <v>-7.26041581994382</v>
+        <v>-7.361676646706581</v>
       </c>
       <c r="GY6" t="n">
-        <v>4.991632120374632</v>
+        <v>4.713473053892223</v>
       </c>
       <c r="GZ6" t="n">
-        <v>-30.6240306716883</v>
+        <v>-31.46646706586822</v>
       </c>
       <c r="HA6" t="n">
-        <v>266.6156871776807</v>
+        <v>257.8505988023953</v>
       </c>
       <c r="HB6" t="n">
-        <v>251.7077654645458</v>
+        <v>244.4673652694612</v>
       </c>
       <c r="HC6" t="n">
-        <v>-28.94559785406565</v>
+        <v>-30.18715568862277</v>
       </c>
       <c r="HD6" t="n">
-        <v>-0.1585304727976849</v>
+        <v>-0.1609435051465694</v>
       </c>
       <c r="HE6" t="n">
-        <v>-0.5578093152933252</v>
+        <v>-0.5622679151500918</v>
       </c>
       <c r="HF6" t="n">
-        <v>-0.07000953484046119</v>
+        <v>-0.0722188955422487</v>
       </c>
       <c r="HG6" t="n">
-        <v>-0.09207341014511738</v>
+        <v>-0.09623586161011299</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.003526134096918251</v>
+        <v>0.002933553885766965</v>
       </c>
       <c r="HI6" t="n">
-        <v>-0.1857200874962828</v>
+        <v>-0.1871892993160439</v>
       </c>
       <c r="HJ6" t="n">
-        <v>-0.2894559785406559</v>
+        <v>-0.3018715568862271</v>
       </c>
       <c r="HK6" t="n">
-        <v>-0.03879534253124817</v>
+        <v>-0.04761642377539599</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.06143869380376205</v>
+        <v>0.06036305322712564</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.3459081370760353</v>
+        <v>0.3366457424065401</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.218842637137751</v>
+        <v>0.2100160080049294</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.003211212394663321</v>
+        <v>0.002434280672923533</v>
       </c>
     </row>
     <row r="7">
@@ -5322,97 +5322,97 @@
         <v>1.826347305389222</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.767365269461078</v>
+        <v>1.761377245508982</v>
       </c>
       <c r="BO8" t="n">
-        <v>28.27784431137725</v>
+        <v>28.18203592814372</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.712974051896208</v>
+        <v>4.697005988023952</v>
       </c>
       <c r="BQ8" t="n">
-        <v>110.1657684630739</v>
+        <v>109.7925149700599</v>
       </c>
       <c r="BR8" t="n">
-        <v>32.40169660678643</v>
+        <v>32.29191616766467</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.19331337325349</v>
+        <v>11.15538922155689</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.12974051896208</v>
+        <v>46.97005988023952</v>
       </c>
       <c r="BU8" t="n">
-        <v>1476.339121756487</v>
+        <v>1471.337125748503</v>
       </c>
       <c r="BV8" t="n">
-        <v>51.25359281437126</v>
+        <v>51.07994011976048</v>
       </c>
       <c r="BW8" t="n">
-        <v>22.97574850299401</v>
+        <v>22.89790419161677</v>
       </c>
       <c r="BX8" t="n">
-        <v>22.97574850299401</v>
+        <v>22.89790419161677</v>
       </c>
       <c r="BY8" t="n">
-        <v>73.05109780439123</v>
+        <v>72.80359281437127</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.534730538922156</v>
+        <v>3.522754491017964</v>
       </c>
       <c r="CA8" t="n">
-        <v>23.56487025948104</v>
+        <v>23.48502994011976</v>
       </c>
       <c r="CB8" t="n">
-        <v>41.23852295409182</v>
+        <v>41.09880239520958</v>
       </c>
       <c r="CC8" t="n">
-        <v>177.3256487025948</v>
+        <v>176.7248502994012</v>
       </c>
       <c r="CD8" t="n">
-        <v>1161.158982035928</v>
+        <v>1157.224850299401</v>
       </c>
       <c r="CE8" t="n">
-        <v>926.0994011976048</v>
+        <v>922.9616766467066</v>
       </c>
       <c r="CF8" t="n">
-        <v>228.6970658682635</v>
+        <v>227.9222155688623</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.1377167742437204</v>
+        <v>0.1372501749747259</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.4162106954921327</v>
+        <v>0.414800528812505</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.4442763380370776</v>
+        <v>0.4427710819366639</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.077127961063785</v>
+        <v>1.073478535479967</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.1289760322714704</v>
+        <v>0.1285390475780213</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.485948024985306</v>
+        <v>0.4843015807197282</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.286970658682635</v>
+        <v>2.279222155688623</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.115453012371675</v>
+        <v>1.111673737384815</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.1151489936750059</v>
+        <v>0.1147588564780721</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.106924004325601</v>
+        <v>1.103173626536932</v>
       </c>
       <c r="CQ8" t="n">
-        <v>1.178441776443361</v>
+        <v>1.174449088737302</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.1580952931560372</v>
+        <v>0.157559649269349</v>
       </c>
       <c r="CS8" t="n">
         <v>0</v>
@@ -5610,190 +5610,190 @@
         <v>1.736526946107784</v>
       </c>
       <c r="FF8" t="n">
-        <v>2.503503400438941</v>
+        <v>2.495808383233533</v>
       </c>
       <c r="FG8" t="n">
-        <v>24.40915815427967</v>
+        <v>24.33413173652695</v>
       </c>
       <c r="FH8" t="n">
-        <v>8.762261901536293</v>
+        <v>8.735329341317366</v>
       </c>
       <c r="FI8" t="n">
-        <v>98.88838431733816</v>
+        <v>98.58443113772455</v>
       </c>
       <c r="FJ8" t="n">
-        <v>31.9196683555965</v>
+        <v>31.82155688622754</v>
       </c>
       <c r="FK8" t="n">
-        <v>8.762261901536293</v>
+        <v>8.735329341317366</v>
       </c>
       <c r="FL8" t="n">
-        <v>38.80430270680358</v>
+        <v>38.68502994011976</v>
       </c>
       <c r="FM8" t="n">
-        <v>1369.416360040101</v>
+        <v>1365.207185628743</v>
       </c>
       <c r="FN8" t="n">
-        <v>63.21346086108326</v>
+        <v>63.0191616766467</v>
       </c>
       <c r="FO8" t="n">
-        <v>22.53153060395047</v>
+        <v>22.4622754491018</v>
       </c>
       <c r="FP8" t="n">
-        <v>22.53153060395047</v>
+        <v>22.4622754491018</v>
       </c>
       <c r="FQ8" t="n">
-        <v>84.49323976481426</v>
+        <v>84.23353293413174</v>
       </c>
       <c r="FR8" t="n">
-        <v>6.258758501097352</v>
+        <v>6.239520958083832</v>
       </c>
       <c r="FS8" t="n">
-        <v>36.30079930636465</v>
+        <v>36.18922155688622</v>
       </c>
       <c r="FT8" t="n">
-        <v>38.17842685669385</v>
+        <v>38.06107784431138</v>
       </c>
       <c r="FU8" t="n">
-        <v>168.9864795296285</v>
+        <v>168.4670658682635</v>
       </c>
       <c r="FV8" t="n">
-        <v>1026.436394179966</v>
+        <v>1023.281437125749</v>
       </c>
       <c r="FW8" t="n">
-        <v>800.4952122903514</v>
+        <v>798.0347305389222</v>
       </c>
       <c r="FX8" t="n">
-        <v>240.8370271222261</v>
+        <v>240.0967664670659</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.3911724063185845</v>
+        <v>0.3899700598802395</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.9893652861350044</v>
+        <v>0.9863242745278672</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.177331490864425</v>
+        <v>0.1767864271457086</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.8940206996175335</v>
+        <v>0.8912727486204062</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.1116732958648399</v>
+        <v>0.1113300457087132</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.5384758854028485</v>
+        <v>0.5368207723312444</v>
       </c>
       <c r="GE8" t="n">
-        <v>2.408370271222261</v>
+        <v>2.400967664670659</v>
       </c>
       <c r="GF8" t="n">
-        <v>1.420037899077647</v>
+        <v>1.415673129265943</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.112900039489927</v>
+        <v>0.1125530186925061</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.9852281294560559</v>
+        <v>0.9821998342254254</v>
       </c>
       <c r="GI8" t="n">
-        <v>1.099963563155067</v>
+        <v>1.096582605676712</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.1359740108662313</v>
+        <v>0.135556067614019</v>
       </c>
       <c r="GK8" t="n">
-        <v>-0.736138130977863</v>
+        <v>-0.7344311377245509</v>
       </c>
       <c r="GL8" t="n">
-        <v>3.868686157097574</v>
+        <v>3.84790419161677</v>
       </c>
       <c r="GM8" t="n">
-        <v>-4.049287849640085</v>
+        <v>-4.038323353293413</v>
       </c>
       <c r="GN8" t="n">
-        <v>11.2773841457357</v>
+        <v>11.20808383233533</v>
       </c>
       <c r="GO8" t="n">
-        <v>0.4820282511899343</v>
+        <v>0.4703592814371298</v>
       </c>
       <c r="GP8" t="n">
-        <v>2.4310514717172</v>
+        <v>2.420059880239521</v>
       </c>
       <c r="GQ8" t="n">
-        <v>8.325437812158498</v>
+        <v>8.285029940119763</v>
       </c>
       <c r="GR8" t="n">
-        <v>106.9227617163865</v>
+        <v>106.1299401197605</v>
       </c>
       <c r="GS8" t="n">
-        <v>-11.959868046712</v>
+        <v>-11.93922155688622</v>
       </c>
       <c r="GT8" t="n">
-        <v>0.4442178990435437</v>
+        <v>0.4356287425149716</v>
       </c>
       <c r="GU8" t="n">
-        <v>0.4442178990435437</v>
+        <v>0.4356287425149716</v>
       </c>
       <c r="GV8" t="n">
-        <v>-11.44214196042303</v>
+        <v>-11.42994011976047</v>
       </c>
       <c r="GW8" t="n">
-        <v>-2.724027962175196</v>
+        <v>-2.716766467065868</v>
       </c>
       <c r="GX8" t="n">
-        <v>-12.73592904688361</v>
+        <v>-12.70419161676646</v>
       </c>
       <c r="GY8" t="n">
-        <v>3.060096097397974</v>
+        <v>3.037724550898204</v>
       </c>
       <c r="GZ8" t="n">
-        <v>8.339169172966308</v>
+        <v>8.257784431137736</v>
       </c>
       <c r="HA8" t="n">
-        <v>134.7225878559623</v>
+        <v>133.9434131736526</v>
       </c>
       <c r="HB8" t="n">
-        <v>125.6041889072534</v>
+        <v>124.9269461077844</v>
       </c>
       <c r="HC8" t="n">
-        <v>-12.13996125396261</v>
+        <v>-12.17455089820356</v>
       </c>
       <c r="HD8" t="n">
-        <v>-0.2534556320748642</v>
+        <v>-0.2527198849055137</v>
       </c>
       <c r="HE8" t="n">
-        <v>-0.5731545906428717</v>
+        <v>-0.5715237457153622</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.2669448471726525</v>
+        <v>0.2659846547909553</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.1831072614462517</v>
+        <v>0.1822057868595612</v>
       </c>
       <c r="HH8" t="n">
-        <v>0.01730273640663045</v>
+        <v>0.01720900186930818</v>
       </c>
       <c r="HI8" t="n">
-        <v>-0.05252786041754248</v>
+        <v>-0.05251919161151619</v>
       </c>
       <c r="HJ8" t="n">
-        <v>-0.1213996125396264</v>
+        <v>-0.1217455089820363</v>
       </c>
       <c r="HK8" t="n">
-        <v>-0.3045848867059722</v>
+        <v>-0.3039993918811281</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.002248954185078936</v>
+        <v>0.002205837785566045</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.1216958748695451</v>
+        <v>0.1209737923115068</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.07847821328829463</v>
+        <v>0.07786648306059019</v>
       </c>
       <c r="HO8" t="n">
-        <v>0.02212128228980595</v>
+        <v>0.02200358165532998</v>
       </c>
     </row>
     <row r="9">
@@ -5993,97 +5993,97 @@
         <v>5</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.06579375186279</v>
+        <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>31.54212750968651</v>
+        <v>31.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>11.72720125360139</v>
+        <v>11.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>146.7922087950795</v>
+        <v>145.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>16.57983625509162</v>
+        <v>16.4</v>
       </c>
       <c r="BS9" t="n">
-        <v>14.15351875434651</v>
+        <v>14</v>
       </c>
       <c r="BT9" t="n">
-        <v>32.35090000993488</v>
+        <v>32</v>
       </c>
       <c r="BU9" t="n">
-        <v>1860.985523071504</v>
+        <v>1840.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>31.9465137598107</v>
+        <v>31.6</v>
       </c>
       <c r="BW9" t="n">
-        <v>14.15351875434651</v>
+        <v>14</v>
       </c>
       <c r="BX9" t="n">
-        <v>12.53597375384977</v>
+        <v>12.4</v>
       </c>
       <c r="BY9" t="n">
-        <v>19.81492625608512</v>
+        <v>19.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.213158750372558</v>
+        <v>1.2</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.492111252607907</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="n">
-        <v>27.90265125856884</v>
+        <v>27.6</v>
       </c>
       <c r="CC9" t="n">
-        <v>97.45708627992884</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="CD9" t="n">
-        <v>1655.961694258542</v>
+        <v>1638</v>
       </c>
       <c r="CE9" t="n">
-        <v>1514.022120464952</v>
+        <v>1497.6</v>
       </c>
       <c r="CF9" t="n">
-        <v>184.7236390567282</v>
+        <v>182.72</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.5036446933364863</v>
+        <v>0.4981818181818182</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.8675923184482537</v>
+        <v>0.8581818181818182</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.1960211737476213</v>
+        <v>0.1938949938949939</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.4507993240090133</v>
+        <v>0.4459096459096459</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.03927065868697838</v>
+        <v>0.03884470223695138</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.1209037400786297</v>
+        <v>0.1195923353392955</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.847236390567282</v>
+        <v>1.8272</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.9827227760954425</v>
+        <v>0.972063492063492</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.1607419592164894</v>
+        <v>0.1589984418779085</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.471470960747788</v>
+        <v>1.455510379292969</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.390518734336651</v>
+        <v>1.375436216151886</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.05600390770797717</v>
+        <v>0.05539645098296839</v>
       </c>
       <c r="CS9" t="n">
         <v>0</v>
@@ -6281,190 +6281,190 @@
         <v>2.889221556886227</v>
       </c>
       <c r="FF9" t="n">
-        <v>5.554127040037573</v>
+        <v>5.538922155688622</v>
       </c>
       <c r="FG9" t="n">
-        <v>43.87760361629682</v>
+        <v>43.75748502994012</v>
       </c>
       <c r="FH9" t="n">
-        <v>12.21907948808266</v>
+        <v>12.18562874251497</v>
       </c>
       <c r="FI9" t="n">
-        <v>150.5168427850182</v>
+        <v>150.1047904191617</v>
       </c>
       <c r="FJ9" t="n">
-        <v>34.43558764823295</v>
+        <v>34.34131736526946</v>
       </c>
       <c r="FK9" t="n">
-        <v>18.32861923212399</v>
+        <v>18.27844311377245</v>
       </c>
       <c r="FL9" t="n">
-        <v>59.42915932840202</v>
+        <v>59.26646706586826</v>
       </c>
       <c r="FM9" t="n">
-        <v>1787.873494188095</v>
+        <v>1782.979041916167</v>
       </c>
       <c r="FN9" t="n">
-        <v>42.76677820828931</v>
+        <v>42.64970059880239</v>
       </c>
       <c r="FO9" t="n">
-        <v>29.99228601620289</v>
+        <v>29.91017964071856</v>
       </c>
       <c r="FP9" t="n">
-        <v>31.65852412821416</v>
+        <v>31.57185628742515</v>
       </c>
       <c r="FQ9" t="n">
-        <v>62.20622284842081</v>
+        <v>62.03592814371257</v>
       </c>
       <c r="FR9" t="n">
-        <v>4.998714336033816</v>
+        <v>4.985029940119761</v>
       </c>
       <c r="FS9" t="n">
-        <v>17.21779382411648</v>
+        <v>17.17065868263473</v>
       </c>
       <c r="FT9" t="n">
-        <v>42.21136550428555</v>
+        <v>42.09580838323352</v>
       </c>
       <c r="FU9" t="n">
-        <v>153.293906305037</v>
+        <v>152.874251497006</v>
       </c>
       <c r="FV9" t="n">
-        <v>1467.400363977927</v>
+        <v>1463.383233532934</v>
       </c>
       <c r="FW9" t="n">
-        <v>1220.797123400258</v>
+        <v>1217.455089820359</v>
       </c>
       <c r="FX9" t="n">
-        <v>230.8850610543619</v>
+        <v>230.2529940119761</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.4740160146238963</v>
+        <v>0.4727183563906669</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.7956659388007848</v>
+        <v>0.7934877371693395</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.2047733706680519</v>
+        <v>0.2042127865481159</v>
       </c>
       <c r="GB9" t="n">
-        <v>1.200589077341455</v>
+        <v>1.197302364967035</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.1118016101832083</v>
+        <v>0.1114955439840365</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.2912081170069509</v>
+        <v>0.2904109105857351</v>
       </c>
       <c r="GE9" t="n">
-        <v>2.308850610543619</v>
+        <v>2.302529940119761</v>
       </c>
       <c r="GF9" t="n">
-        <v>1.18429172148757</v>
+        <v>1.181049624479195</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.1607419163031171</v>
+        <v>0.1603018719487479</v>
       </c>
       <c r="GH9" t="n">
-        <v>1.502088554267333</v>
+        <v>1.497976462018654</v>
       </c>
       <c r="GI9" t="n">
-        <v>1.48746632461726</v>
+        <v>1.483394261937432</v>
       </c>
       <c r="GJ9" t="n">
-        <v>0.1448437684670038</v>
+        <v>0.1444472466135548</v>
       </c>
       <c r="GK9" t="n">
-        <v>0.5116667118252174</v>
+        <v>0.4610778443113777</v>
       </c>
       <c r="GL9" t="n">
-        <v>-12.33547610661032</v>
+        <v>-12.55748502994012</v>
       </c>
       <c r="GM9" t="n">
-        <v>-0.4918782344812662</v>
+        <v>-0.5856287425149702</v>
       </c>
       <c r="GN9" t="n">
-        <v>-3.724633989938695</v>
+        <v>-4.904790419161685</v>
       </c>
       <c r="GO9" t="n">
-        <v>-17.85575139314133</v>
+        <v>-17.94131736526946</v>
       </c>
       <c r="GP9" t="n">
-        <v>-4.175100477777477</v>
+        <v>-4.278443113772454</v>
       </c>
       <c r="GQ9" t="n">
-        <v>-27.07825931846714</v>
+        <v>-27.26646706586826</v>
       </c>
       <c r="GR9" t="n">
-        <v>73.11202888340949</v>
+        <v>57.82095808383247</v>
       </c>
       <c r="GS9" t="n">
-        <v>-10.82026444847861</v>
+        <v>-11.04970059880239</v>
       </c>
       <c r="GT9" t="n">
-        <v>-15.83876726185638</v>
+        <v>-15.91017964071856</v>
       </c>
       <c r="GU9" t="n">
-        <v>-19.1225503743644</v>
+        <v>-19.17185628742515</v>
       </c>
       <c r="GV9" t="n">
-        <v>-42.39129659233569</v>
+        <v>-42.43592814371257</v>
       </c>
       <c r="GW9" t="n">
-        <v>-3.785555585661258</v>
+        <v>-3.78502994011976</v>
       </c>
       <c r="GX9" t="n">
-        <v>-8.725682571508569</v>
+        <v>-8.77065868263473</v>
       </c>
       <c r="GY9" t="n">
-        <v>-14.30871424571671</v>
+        <v>-14.49580838323352</v>
       </c>
       <c r="GZ9" t="n">
-        <v>-55.83682002510817</v>
+        <v>-56.47425149700598</v>
       </c>
       <c r="HA9" t="n">
-        <v>188.561330280615</v>
+        <v>174.6167664670661</v>
       </c>
       <c r="HB9" t="n">
-        <v>293.224997064694</v>
+        <v>280.1449101796406</v>
       </c>
       <c r="HC9" t="n">
-        <v>-46.16142199763374</v>
+        <v>-47.53299401197609</v>
       </c>
       <c r="HD9" t="n">
-        <v>0.02962867871259001</v>
+        <v>0.02546346179115128</v>
       </c>
       <c r="HE9" t="n">
-        <v>0.07192637964746884</v>
+        <v>0.06469408101247864</v>
       </c>
       <c r="HF9" t="n">
-        <v>-0.00875219692043061</v>
+        <v>-0.01031779265312199</v>
       </c>
       <c r="HG9" t="n">
-        <v>-0.7497897533324416</v>
+        <v>-0.7513927190573895</v>
       </c>
       <c r="HH9" t="n">
-        <v>-0.07253095149622996</v>
+        <v>-0.07265084174708507</v>
       </c>
       <c r="HI9" t="n">
-        <v>-0.1703043769283212</v>
+        <v>-0.1708185752464397</v>
       </c>
       <c r="HJ9" t="n">
-        <v>-0.4616142199763371</v>
+        <v>-0.4753299401197606</v>
       </c>
       <c r="HK9" t="n">
-        <v>-0.2015689453921272</v>
+        <v>-0.2089861324157033</v>
       </c>
       <c r="HL9" t="n">
-        <v>4.291337235562409e-08</v>
+        <v>-0.001303430070839412</v>
       </c>
       <c r="HM9" t="n">
-        <v>-0.03061759351954474</v>
+        <v>-0.04246608272568531</v>
       </c>
       <c r="HN9" t="n">
-        <v>-0.0969475902806094</v>
+        <v>-0.107958045785546</v>
       </c>
       <c r="HO9" t="n">
-        <v>-0.08883986075902661</v>
+        <v>-0.08905079563058638</v>
       </c>
     </row>
     <row r="10">
@@ -6664,97 +6664,97 @@
         <v>2.537425149700599</v>
       </c>
       <c r="BN10" t="n">
-        <v>3.194437369604682</v>
+        <v>3.145508982035928</v>
       </c>
       <c r="BO10" t="n">
-        <v>26.62031141337235</v>
+        <v>26.2125748502994</v>
       </c>
       <c r="BP10" t="n">
-        <v>10.64812456534894</v>
+        <v>10.48502994011976</v>
       </c>
       <c r="BQ10" t="n">
-        <v>122.4534325015128</v>
+        <v>120.5778443113772</v>
       </c>
       <c r="BR10" t="n">
-        <v>22.89346781550022</v>
+        <v>22.54281437125749</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.518499652279152</v>
+        <v>8.388023952095809</v>
       </c>
       <c r="BT10" t="n">
-        <v>29.28234255470959</v>
+        <v>28.83383233532934</v>
       </c>
       <c r="BU10" t="n">
-        <v>1540.783624605991</v>
+        <v>1517.183832335329</v>
       </c>
       <c r="BV10" t="n">
-        <v>35.1388110656515</v>
+        <v>34.60059880239521</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.50459307629086</v>
+        <v>16.25179640718563</v>
       </c>
       <c r="BX10" t="n">
-        <v>21.82865535896532</v>
+        <v>21.49431137724551</v>
       </c>
       <c r="BY10" t="n">
-        <v>67.08318476169832</v>
+        <v>66.05568862275449</v>
       </c>
       <c r="BZ10" t="n">
-        <v>5.32406228267447</v>
+        <v>5.24251497005988</v>
       </c>
       <c r="CA10" t="n">
-        <v>23.95828027203511</v>
+        <v>23.59131736526946</v>
       </c>
       <c r="CB10" t="n">
-        <v>42.59249826139576</v>
+        <v>41.94011976047904</v>
       </c>
       <c r="CC10" t="n">
-        <v>153.3329937410248</v>
+        <v>150.9844311377246</v>
       </c>
       <c r="CD10" t="n">
-        <v>1281.501791439745</v>
+        <v>1261.873353293413</v>
       </c>
       <c r="CE10" t="n">
-        <v>1073.863362415441</v>
+        <v>1057.415269461078</v>
       </c>
       <c r="CF10" t="n">
-        <v>220.0967347657626</v>
+        <v>216.7255688622754</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.3046546750641502</v>
+        <v>0.2999883566200931</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.9938249594325678</v>
+        <v>0.9786027944111777</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.2920167494436604</v>
+        <v>0.2875440029032844</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.098577613435838</v>
+        <v>1.081750978562356</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.05654997515305848</v>
+        <v>0.0556838135160768</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.3362754259127935</v>
+        <v>0.3311247804421812</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.200967347657626</v>
+        <v>2.167255688622755</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.413352149492426</v>
+        <v>1.391704192828917</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.09975305061169019</v>
+        <v>0.09822515841761087</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.225215076329026</v>
+        <v>1.20644876753233</v>
       </c>
       <c r="CQ10" t="n">
-        <v>1.244637490623956</v>
+        <v>1.225573693630063</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.07339386286644824</v>
+        <v>0.07226970767039818</v>
       </c>
       <c r="CS10" t="n">
         <v>1</v>
@@ -6952,190 +6952,190 @@
         <v>3.368263473053892</v>
       </c>
       <c r="FF10" t="n">
-        <v>3.651087869509849</v>
+        <v>3.657185628742515</v>
       </c>
       <c r="FG10" t="n">
-        <v>37.03246267645704</v>
+        <v>37.09431137724551</v>
       </c>
       <c r="FH10" t="n">
-        <v>11.99643157124665</v>
+        <v>12.01646706586826</v>
       </c>
       <c r="FI10" t="n">
-        <v>135.611835153223</v>
+        <v>135.8383233532934</v>
       </c>
       <c r="FJ10" t="n">
-        <v>40.16196656460835</v>
+        <v>40.22904191616767</v>
       </c>
       <c r="FK10" t="n">
-        <v>17.7338553661907</v>
+        <v>17.76347305389222</v>
       </c>
       <c r="FL10" t="n">
-        <v>53.72315007993065</v>
+        <v>53.81287425149701</v>
       </c>
       <c r="FM10" t="n">
-        <v>1543.367000839949</v>
+        <v>1545.944610778443</v>
       </c>
       <c r="FN10" t="n">
-        <v>39.11879860189124</v>
+        <v>39.18413173652695</v>
       </c>
       <c r="FO10" t="n">
-        <v>15.6475194407565</v>
+        <v>15.67365269461078</v>
       </c>
       <c r="FP10" t="n">
-        <v>21.38494323570055</v>
+        <v>21.42065868263473</v>
       </c>
       <c r="FQ10" t="n">
-        <v>61.02532581895034</v>
+        <v>61.12724550898204</v>
       </c>
       <c r="FR10" t="n">
-        <v>3.651087869509849</v>
+        <v>3.657185628742515</v>
       </c>
       <c r="FS10" t="n">
-        <v>15.12593545939795</v>
+        <v>15.15119760479042</v>
       </c>
       <c r="FT10" t="n">
-        <v>37.5540466578156</v>
+        <v>37.61676646706587</v>
       </c>
       <c r="FU10" t="n">
-        <v>128.8312433955618</v>
+        <v>129.0464071856287</v>
       </c>
       <c r="FV10" t="n">
-        <v>1278.923922291164</v>
+        <v>1281.059880239521</v>
       </c>
       <c r="FW10" t="n">
-        <v>1075.50616956133</v>
+        <v>1077.302395209581</v>
       </c>
       <c r="FX10" t="n">
-        <v>217.7091538190587</v>
+        <v>218.072754491018</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.2489175457268231</v>
+        <v>0.2493332681955437</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.9181620737893261</v>
+        <v>0.9196955157284499</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.09483345115609998</v>
+        <v>0.0949918345127926</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.7768237571624464</v>
+        <v>0.7781211469834225</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.1110685525629577</v>
+        <v>0.1112540505065995</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.271356353585656</v>
+        <v>0.2718095515829536</v>
       </c>
       <c r="GE10" t="n">
-        <v>2.177091538190587</v>
+        <v>2.180727544910179</v>
       </c>
       <c r="GF10" t="n">
-        <v>1.378804000632317</v>
+        <v>1.381106770416387</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.1198333769504246</v>
+        <v>0.1200335132130391</v>
       </c>
       <c r="GH10" t="n">
-        <v>1.357511683868086</v>
+        <v>1.359778892902655</v>
       </c>
       <c r="GI10" t="n">
-        <v>1.347728598293713</v>
+        <v>1.34997946838972</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.1483443906599942</v>
+        <v>0.1485921437708725</v>
       </c>
       <c r="GK10" t="n">
-        <v>-0.4566504999051673</v>
+        <v>-0.511676646706587</v>
       </c>
       <c r="GL10" t="n">
-        <v>-10.4121512630847</v>
+        <v>-10.88173652694611</v>
       </c>
       <c r="GM10" t="n">
-        <v>-1.348307005897707</v>
+        <v>-1.531437125748502</v>
       </c>
       <c r="GN10" t="n">
-        <v>-13.15840265171018</v>
+        <v>-15.26047904191617</v>
       </c>
       <c r="GO10" t="n">
-        <v>-17.26849874910813</v>
+        <v>-17.68622754491018</v>
       </c>
       <c r="GP10" t="n">
-        <v>-9.215355713911544</v>
+        <v>-9.375449101796407</v>
       </c>
       <c r="GQ10" t="n">
-        <v>-24.44080752522106</v>
+        <v>-24.97904191616767</v>
       </c>
       <c r="GR10" t="n">
-        <v>-2.583376233957551</v>
+        <v>-28.76077844311385</v>
       </c>
       <c r="GS10" t="n">
-        <v>-3.97998753623974</v>
+        <v>-4.583532934131739</v>
       </c>
       <c r="GT10" t="n">
-        <v>0.8570736355343591</v>
+        <v>0.5781437125748496</v>
       </c>
       <c r="GU10" t="n">
-        <v>0.4437121232647776</v>
+        <v>0.07365269461077872</v>
       </c>
       <c r="GV10" t="n">
-        <v>6.057858942747984</v>
+        <v>4.928443113772452</v>
       </c>
       <c r="GW10" t="n">
-        <v>1.672974413164621</v>
+        <v>1.585329341317365</v>
       </c>
       <c r="GX10" t="n">
-        <v>8.832344812637167</v>
+        <v>8.440119760479041</v>
       </c>
       <c r="GY10" t="n">
-        <v>5.038451603580164</v>
+        <v>4.32335329341317</v>
       </c>
       <c r="GZ10" t="n">
-        <v>24.50175034546291</v>
+        <v>21.93802395209582</v>
       </c>
       <c r="HA10" t="n">
-        <v>2.577869148580476</v>
+        <v>-19.18652694610773</v>
       </c>
       <c r="HB10" t="n">
-        <v>-1.642807145889265</v>
+        <v>-19.88712574850319</v>
       </c>
       <c r="HC10" t="n">
-        <v>2.387580946703821</v>
+        <v>-1.347185628742551</v>
       </c>
       <c r="HD10" t="n">
-        <v>0.05573712933732711</v>
+        <v>0.05065508842454944</v>
       </c>
       <c r="HE10" t="n">
-        <v>0.07566288564324164</v>
+        <v>0.05890727868272783</v>
       </c>
       <c r="HF10" t="n">
-        <v>0.1971832982875604</v>
+        <v>0.1925521683904918</v>
       </c>
       <c r="HG10" t="n">
-        <v>0.3217538562733916</v>
+        <v>0.3036298315789333</v>
       </c>
       <c r="HH10" t="n">
-        <v>-0.05451857740989917</v>
+        <v>-0.05557023699052265</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.06491907232713756</v>
+        <v>0.05931522885922769</v>
       </c>
       <c r="HJ10" t="n">
-        <v>0.02387580946703904</v>
+        <v>-0.01347185628742453</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.03454814886010982</v>
+        <v>0.01059742241253048</v>
       </c>
       <c r="HL10" t="n">
-        <v>-0.02008032633873437</v>
+        <v>-0.02180835479542823</v>
       </c>
       <c r="HM10" t="n">
-        <v>-0.1322966075390601</v>
+        <v>-0.1533301253703252</v>
       </c>
       <c r="HN10" t="n">
-        <v>-0.1030911076697569</v>
+        <v>-0.1244057747596572</v>
       </c>
       <c r="HO10" t="n">
-        <v>-0.07495052779354593</v>
+        <v>-0.0763224361004743</v>
       </c>
     </row>
   </sheetData>
